--- a/blok_1/lid_sdel_all.xlsx
+++ b/blok_1/lid_sdel_all.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL406"/>
+  <dimension ref="A1:AM406"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -609,6 +609,11 @@
       <c r="AL1" t="inlineStr">
         <is>
           <t>flag_sdelka</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>flag_sdelka_success</t>
         </is>
       </c>
     </row>
@@ -699,6 +704,7 @@
       <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -785,6 +791,7 @@
       <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -879,6 +886,7 @@
       <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -973,6 +981,7 @@
       <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1043,6 +1052,7 @@
       <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1133,6 +1143,7 @@
       <c r="AJ7" t="inlineStr"/>
       <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1227,6 +1238,7 @@
       <c r="AJ8" t="inlineStr"/>
       <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1297,6 +1309,7 @@
       <c r="AJ9" t="inlineStr"/>
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1367,6 +1380,7 @@
       <c r="AJ10" t="inlineStr"/>
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1439,6 +1453,7 @@
       <c r="AJ11" t="inlineStr"/>
       <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1533,6 +1548,7 @@
       <c r="AJ12" t="inlineStr"/>
       <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1627,6 +1643,7 @@
       <c r="AJ13" t="inlineStr"/>
       <c r="AK13" t="inlineStr"/>
       <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1713,6 +1730,7 @@
       <c r="AJ14" t="inlineStr"/>
       <c r="AK14" t="inlineStr"/>
       <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1783,6 +1801,7 @@
       <c r="AJ15" t="inlineStr"/>
       <c r="AK15" t="inlineStr"/>
       <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1857,6 +1876,7 @@
       <c r="AJ16" t="inlineStr"/>
       <c r="AK16" t="inlineStr"/>
       <c r="AL16" t="inlineStr"/>
+      <c r="AM16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1951,6 +1971,7 @@
       <c r="AJ17" t="inlineStr"/>
       <c r="AK17" t="inlineStr"/>
       <c r="AL17" t="inlineStr"/>
+      <c r="AM17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2045,6 +2066,7 @@
       <c r="AJ18" t="inlineStr"/>
       <c r="AK18" t="inlineStr"/>
       <c r="AL18" t="inlineStr"/>
+      <c r="AM18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2131,6 +2153,7 @@
       <c r="AJ19" t="inlineStr"/>
       <c r="AK19" t="inlineStr"/>
       <c r="AL19" t="inlineStr"/>
+      <c r="AM19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2227,6 +2250,7 @@
       <c r="AJ20" t="inlineStr"/>
       <c r="AK20" t="inlineStr"/>
       <c r="AL20" t="inlineStr"/>
+      <c r="AM20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2297,6 +2321,7 @@
       <c r="AJ21" t="inlineStr"/>
       <c r="AK21" t="inlineStr"/>
       <c r="AL21" t="inlineStr"/>
+      <c r="AM21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2391,6 +2416,7 @@
       <c r="AJ22" t="inlineStr"/>
       <c r="AK22" t="inlineStr"/>
       <c r="AL22" t="inlineStr"/>
+      <c r="AM22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2487,6 +2513,7 @@
       <c r="AJ23" t="inlineStr"/>
       <c r="AK23" t="inlineStr"/>
       <c r="AL23" t="inlineStr"/>
+      <c r="AM23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2573,6 +2600,7 @@
       <c r="AJ24" t="inlineStr"/>
       <c r="AK24" t="inlineStr"/>
       <c r="AL24" t="inlineStr"/>
+      <c r="AM24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2661,6 +2689,7 @@
       <c r="AJ25" t="inlineStr"/>
       <c r="AK25" t="inlineStr"/>
       <c r="AL25" t="inlineStr"/>
+      <c r="AM25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2731,6 +2760,7 @@
       <c r="AJ26" t="inlineStr"/>
       <c r="AK26" t="inlineStr"/>
       <c r="AL26" t="inlineStr"/>
+      <c r="AM26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2801,6 +2831,7 @@
       <c r="AJ27" t="inlineStr"/>
       <c r="AK27" t="inlineStr"/>
       <c r="AL27" t="inlineStr"/>
+      <c r="AM27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2936,6 +2967,9 @@
       </c>
       <c r="AL28" t="n">
         <v>1</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -3009,6 +3043,7 @@
       <c r="AJ29" t="inlineStr"/>
       <c r="AK29" t="inlineStr"/>
       <c r="AL29" t="inlineStr"/>
+      <c r="AM29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3079,6 +3114,7 @@
       <c r="AJ30" t="inlineStr"/>
       <c r="AK30" t="inlineStr"/>
       <c r="AL30" t="inlineStr"/>
+      <c r="AM30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3173,6 +3209,7 @@
       <c r="AJ31" t="inlineStr"/>
       <c r="AK31" t="inlineStr"/>
       <c r="AL31" t="inlineStr"/>
+      <c r="AM31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3245,6 +3282,7 @@
       <c r="AJ32" t="inlineStr"/>
       <c r="AK32" t="inlineStr"/>
       <c r="AL32" t="inlineStr"/>
+      <c r="AM32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3317,6 +3355,7 @@
       <c r="AJ33" t="inlineStr"/>
       <c r="AK33" t="inlineStr"/>
       <c r="AL33" t="inlineStr"/>
+      <c r="AM33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3407,6 +3446,7 @@
       <c r="AJ34" t="inlineStr"/>
       <c r="AK34" t="inlineStr"/>
       <c r="AL34" t="inlineStr"/>
+      <c r="AM34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3501,6 +3541,7 @@
       <c r="AJ35" t="inlineStr"/>
       <c r="AK35" t="inlineStr"/>
       <c r="AL35" t="inlineStr"/>
+      <c r="AM35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -3573,6 +3614,7 @@
       <c r="AJ36" t="inlineStr"/>
       <c r="AK36" t="inlineStr"/>
       <c r="AL36" t="inlineStr"/>
+      <c r="AM36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -3663,6 +3705,7 @@
       <c r="AJ37" t="inlineStr"/>
       <c r="AK37" t="inlineStr"/>
       <c r="AL37" t="inlineStr"/>
+      <c r="AM37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -3759,6 +3802,7 @@
       <c r="AJ38" t="inlineStr"/>
       <c r="AK38" t="inlineStr"/>
       <c r="AL38" t="inlineStr"/>
+      <c r="AM38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -3895,6 +3939,9 @@
         </is>
       </c>
       <c r="AL39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM39" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3967,6 +4014,7 @@
       <c r="AJ40" t="inlineStr"/>
       <c r="AK40" t="inlineStr"/>
       <c r="AL40" t="inlineStr"/>
+      <c r="AM40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4041,6 +4089,7 @@
       <c r="AJ41" t="inlineStr"/>
       <c r="AK41" t="inlineStr"/>
       <c r="AL41" t="inlineStr"/>
+      <c r="AM41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4173,6 +4222,9 @@
         </is>
       </c>
       <c r="AL42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM42" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4247,6 +4299,7 @@
       <c r="AJ43" t="inlineStr"/>
       <c r="AK43" t="inlineStr"/>
       <c r="AL43" t="inlineStr"/>
+      <c r="AM43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4335,6 +4388,7 @@
       <c r="AJ44" t="inlineStr"/>
       <c r="AK44" t="inlineStr"/>
       <c r="AL44" t="inlineStr"/>
+      <c r="AM44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4431,6 +4485,7 @@
       <c r="AJ45" t="inlineStr"/>
       <c r="AK45" t="inlineStr"/>
       <c r="AL45" t="inlineStr"/>
+      <c r="AM45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -4525,6 +4580,7 @@
       <c r="AJ46" t="inlineStr"/>
       <c r="AK46" t="inlineStr"/>
       <c r="AL46" t="inlineStr"/>
+      <c r="AM46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -4613,6 +4669,7 @@
       <c r="AJ47" t="inlineStr"/>
       <c r="AK47" t="inlineStr"/>
       <c r="AL47" t="inlineStr"/>
+      <c r="AM47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -4749,6 +4806,9 @@
         </is>
       </c>
       <c r="AL48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM48" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4837,6 +4897,7 @@
       <c r="AJ49" t="inlineStr"/>
       <c r="AK49" t="inlineStr"/>
       <c r="AL49" t="inlineStr"/>
+      <c r="AM49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -4973,6 +5034,9 @@
         </is>
       </c>
       <c r="AL50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM50" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5045,6 +5109,7 @@
       <c r="AJ51" t="inlineStr"/>
       <c r="AK51" t="inlineStr"/>
       <c r="AL51" t="inlineStr"/>
+      <c r="AM51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5139,6 +5204,7 @@
       <c r="AJ52" t="inlineStr"/>
       <c r="AK52" t="inlineStr"/>
       <c r="AL52" t="inlineStr"/>
+      <c r="AM52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5211,6 +5277,7 @@
       <c r="AJ53" t="inlineStr"/>
       <c r="AK53" t="inlineStr"/>
       <c r="AL53" t="inlineStr"/>
+      <c r="AM53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5297,6 +5364,7 @@
       <c r="AJ54" t="inlineStr"/>
       <c r="AK54" t="inlineStr"/>
       <c r="AL54" t="inlineStr"/>
+      <c r="AM54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5369,6 +5437,7 @@
       <c r="AJ55" t="inlineStr"/>
       <c r="AK55" t="inlineStr"/>
       <c r="AL55" t="inlineStr"/>
+      <c r="AM55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -5455,6 +5524,7 @@
       <c r="AJ56" t="inlineStr"/>
       <c r="AK56" t="inlineStr"/>
       <c r="AL56" t="inlineStr"/>
+      <c r="AM56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -5525,6 +5595,7 @@
       <c r="AJ57" t="inlineStr"/>
       <c r="AK57" t="inlineStr"/>
       <c r="AL57" t="inlineStr"/>
+      <c r="AM57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -5599,6 +5670,7 @@
       <c r="AJ58" t="inlineStr"/>
       <c r="AK58" t="inlineStr"/>
       <c r="AL58" t="inlineStr"/>
+      <c r="AM58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -5673,6 +5745,7 @@
       <c r="AJ59" t="inlineStr"/>
       <c r="AK59" t="inlineStr"/>
       <c r="AL59" t="inlineStr"/>
+      <c r="AM59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -5811,6 +5884,9 @@
       <c r="AL60" t="n">
         <v>1</v>
       </c>
+      <c r="AM60" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -5947,6 +6023,9 @@
         </is>
       </c>
       <c r="AL61" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM61" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6027,6 +6106,7 @@
       <c r="AJ62" t="inlineStr"/>
       <c r="AK62" t="inlineStr"/>
       <c r="AL62" t="inlineStr"/>
+      <c r="AM62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6097,6 +6177,7 @@
       <c r="AJ63" t="inlineStr"/>
       <c r="AK63" t="inlineStr"/>
       <c r="AL63" t="inlineStr"/>
+      <c r="AM63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6191,6 +6272,7 @@
       <c r="AJ64" t="inlineStr"/>
       <c r="AK64" t="inlineStr"/>
       <c r="AL64" t="inlineStr"/>
+      <c r="AM64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6285,6 +6367,7 @@
       <c r="AJ65" t="inlineStr"/>
       <c r="AK65" t="inlineStr"/>
       <c r="AL65" t="inlineStr"/>
+      <c r="AM65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -6361,6 +6444,7 @@
       <c r="AJ66" t="inlineStr"/>
       <c r="AK66" t="inlineStr"/>
       <c r="AL66" t="inlineStr"/>
+      <c r="AM66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -6437,6 +6521,7 @@
       <c r="AJ67" t="inlineStr"/>
       <c r="AK67" t="inlineStr"/>
       <c r="AL67" t="inlineStr"/>
+      <c r="AM67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -6511,6 +6596,7 @@
       <c r="AJ68" t="inlineStr"/>
       <c r="AK68" t="inlineStr"/>
       <c r="AL68" t="inlineStr"/>
+      <c r="AM68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -6585,6 +6671,7 @@
       <c r="AJ69" t="inlineStr"/>
       <c r="AK69" t="inlineStr"/>
       <c r="AL69" t="inlineStr"/>
+      <c r="AM69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -6659,6 +6746,7 @@
       <c r="AJ70" t="inlineStr"/>
       <c r="AK70" t="inlineStr"/>
       <c r="AL70" t="inlineStr"/>
+      <c r="AM70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -6749,6 +6837,7 @@
       <c r="AJ71" t="inlineStr"/>
       <c r="AK71" t="inlineStr"/>
       <c r="AL71" t="inlineStr"/>
+      <c r="AM71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -6839,6 +6928,7 @@
       <c r="AJ72" t="inlineStr"/>
       <c r="AK72" t="inlineStr"/>
       <c r="AL72" t="inlineStr"/>
+      <c r="AM72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -6913,6 +7003,7 @@
       <c r="AJ73" t="inlineStr"/>
       <c r="AK73" t="inlineStr"/>
       <c r="AL73" t="inlineStr"/>
+      <c r="AM73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -6983,6 +7074,7 @@
       <c r="AJ74" t="inlineStr"/>
       <c r="AK74" t="inlineStr"/>
       <c r="AL74" t="inlineStr"/>
+      <c r="AM74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7130,6 +7222,9 @@
       <c r="AK75" t="inlineStr"/>
       <c r="AL75" t="n">
         <v>1</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -7225,6 +7320,7 @@
       <c r="AJ76" t="inlineStr"/>
       <c r="AK76" t="inlineStr"/>
       <c r="AL76" t="inlineStr"/>
+      <c r="AM76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -7299,6 +7395,7 @@
       <c r="AJ77" t="inlineStr"/>
       <c r="AK77" t="inlineStr"/>
       <c r="AL77" t="inlineStr"/>
+      <c r="AM77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -7436,6 +7533,9 @@
       </c>
       <c r="AL78" t="n">
         <v>1</v>
+      </c>
+      <c r="AM78" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -7507,6 +7607,7 @@
       <c r="AJ79" t="inlineStr"/>
       <c r="AK79" t="inlineStr"/>
       <c r="AL79" t="inlineStr"/>
+      <c r="AM79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -7641,6 +7742,9 @@
       <c r="AL80" t="n">
         <v>1</v>
       </c>
+      <c r="AM80" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -7777,6 +7881,9 @@
         </is>
       </c>
       <c r="AL81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM81" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7853,6 +7960,7 @@
       <c r="AJ82" t="inlineStr"/>
       <c r="AK82" t="inlineStr"/>
       <c r="AL82" t="inlineStr"/>
+      <c r="AM82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -7939,6 +8047,7 @@
       <c r="AJ83" t="inlineStr"/>
       <c r="AK83" t="inlineStr"/>
       <c r="AL83" t="inlineStr"/>
+      <c r="AM83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8025,6 +8134,7 @@
       <c r="AJ84" t="inlineStr"/>
       <c r="AK84" t="inlineStr"/>
       <c r="AL84" t="inlineStr"/>
+      <c r="AM84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8111,6 +8221,7 @@
       <c r="AJ85" t="inlineStr"/>
       <c r="AK85" t="inlineStr"/>
       <c r="AL85" t="inlineStr"/>
+      <c r="AM85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -8197,6 +8308,7 @@
       <c r="AJ86" t="inlineStr"/>
       <c r="AK86" t="inlineStr"/>
       <c r="AL86" t="inlineStr"/>
+      <c r="AM86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -8267,6 +8379,7 @@
       <c r="AJ87" t="inlineStr"/>
       <c r="AK87" t="inlineStr"/>
       <c r="AL87" t="inlineStr"/>
+      <c r="AM87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -8337,6 +8450,7 @@
       <c r="AJ88" t="inlineStr"/>
       <c r="AK88" t="inlineStr"/>
       <c r="AL88" t="inlineStr"/>
+      <c r="AM88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -8431,6 +8545,7 @@
       <c r="AJ89" t="inlineStr"/>
       <c r="AK89" t="inlineStr"/>
       <c r="AL89" t="inlineStr"/>
+      <c r="AM89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -8501,6 +8616,7 @@
       <c r="AJ90" t="inlineStr"/>
       <c r="AK90" t="inlineStr"/>
       <c r="AL90" t="inlineStr"/>
+      <c r="AM90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -8575,6 +8691,7 @@
       <c r="AJ91" t="inlineStr"/>
       <c r="AK91" t="inlineStr"/>
       <c r="AL91" t="inlineStr"/>
+      <c r="AM91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -8669,6 +8786,7 @@
       <c r="AJ92" t="inlineStr"/>
       <c r="AK92" t="inlineStr"/>
       <c r="AL92" t="inlineStr"/>
+      <c r="AM92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -8763,6 +8881,7 @@
       <c r="AJ93" t="inlineStr"/>
       <c r="AK93" t="inlineStr"/>
       <c r="AL93" t="inlineStr"/>
+      <c r="AM93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -8849,6 +8968,7 @@
       <c r="AJ94" t="inlineStr"/>
       <c r="AK94" t="inlineStr"/>
       <c r="AL94" t="inlineStr"/>
+      <c r="AM94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -8939,6 +9059,7 @@
       <c r="AJ95" t="inlineStr"/>
       <c r="AK95" t="inlineStr"/>
       <c r="AL95" t="inlineStr"/>
+      <c r="AM95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -9029,6 +9150,7 @@
       <c r="AJ96" t="inlineStr"/>
       <c r="AK96" t="inlineStr"/>
       <c r="AL96" t="inlineStr"/>
+      <c r="AM96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -9099,6 +9221,7 @@
       <c r="AJ97" t="inlineStr"/>
       <c r="AK97" t="inlineStr"/>
       <c r="AL97" t="inlineStr"/>
+      <c r="AM97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -9252,6 +9375,9 @@
       </c>
       <c r="AL98" t="n">
         <v>1</v>
+      </c>
+      <c r="AM98" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -9323,6 +9449,7 @@
       <c r="AJ99" t="inlineStr"/>
       <c r="AK99" t="inlineStr"/>
       <c r="AL99" t="inlineStr"/>
+      <c r="AM99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -9417,6 +9544,7 @@
       <c r="AJ100" t="inlineStr"/>
       <c r="AK100" t="inlineStr"/>
       <c r="AL100" t="inlineStr"/>
+      <c r="AM100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -9507,6 +9635,7 @@
       <c r="AJ101" t="inlineStr"/>
       <c r="AK101" t="inlineStr"/>
       <c r="AL101" t="inlineStr"/>
+      <c r="AM101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -9601,6 +9730,7 @@
       <c r="AJ102" t="inlineStr"/>
       <c r="AK102" t="inlineStr"/>
       <c r="AL102" t="inlineStr"/>
+      <c r="AM102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -9693,6 +9823,7 @@
       <c r="AJ103" t="inlineStr"/>
       <c r="AK103" t="inlineStr"/>
       <c r="AL103" t="inlineStr"/>
+      <c r="AM103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -9767,6 +9898,7 @@
       <c r="AJ104" t="inlineStr"/>
       <c r="AK104" t="inlineStr"/>
       <c r="AL104" t="inlineStr"/>
+      <c r="AM104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -9837,6 +9969,7 @@
       <c r="AJ105" t="inlineStr"/>
       <c r="AK105" t="inlineStr"/>
       <c r="AL105" t="inlineStr"/>
+      <c r="AM105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -9907,6 +10040,7 @@
       <c r="AJ106" t="inlineStr"/>
       <c r="AK106" t="inlineStr"/>
       <c r="AL106" t="inlineStr"/>
+      <c r="AM106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -9977,6 +10111,7 @@
       <c r="AJ107" t="inlineStr"/>
       <c r="AK107" t="inlineStr"/>
       <c r="AL107" t="inlineStr"/>
+      <c r="AM107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -10067,6 +10202,7 @@
       <c r="AJ108" t="inlineStr"/>
       <c r="AK108" t="inlineStr"/>
       <c r="AL108" t="inlineStr"/>
+      <c r="AM108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -10137,6 +10273,7 @@
       <c r="AJ109" t="inlineStr"/>
       <c r="AK109" t="inlineStr"/>
       <c r="AL109" t="inlineStr"/>
+      <c r="AM109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -10209,6 +10346,7 @@
       <c r="AJ110" t="inlineStr"/>
       <c r="AK110" t="inlineStr"/>
       <c r="AL110" t="inlineStr"/>
+      <c r="AM110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -10281,6 +10419,7 @@
       <c r="AJ111" t="inlineStr"/>
       <c r="AK111" t="inlineStr"/>
       <c r="AL111" t="inlineStr"/>
+      <c r="AM111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -10353,6 +10492,7 @@
       <c r="AJ112" t="inlineStr"/>
       <c r="AK112" t="inlineStr"/>
       <c r="AL112" t="inlineStr"/>
+      <c r="AM112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -10439,6 +10579,7 @@
       <c r="AJ113" t="inlineStr"/>
       <c r="AK113" t="inlineStr"/>
       <c r="AL113" t="inlineStr"/>
+      <c r="AM113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -10513,6 +10654,7 @@
       <c r="AJ114" t="inlineStr"/>
       <c r="AK114" t="inlineStr"/>
       <c r="AL114" t="inlineStr"/>
+      <c r="AM114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -10587,6 +10729,7 @@
       <c r="AJ115" t="inlineStr"/>
       <c r="AK115" t="inlineStr"/>
       <c r="AL115" t="inlineStr"/>
+      <c r="AM115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -10665,6 +10808,7 @@
       <c r="AJ116" t="inlineStr"/>
       <c r="AK116" t="inlineStr"/>
       <c r="AL116" t="inlineStr"/>
+      <c r="AM116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -10735,6 +10879,7 @@
       <c r="AJ117" t="inlineStr"/>
       <c r="AK117" t="inlineStr"/>
       <c r="AL117" t="inlineStr"/>
+      <c r="AM117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -10825,6 +10970,7 @@
       <c r="AJ118" t="inlineStr"/>
       <c r="AK118" t="inlineStr"/>
       <c r="AL118" t="inlineStr"/>
+      <c r="AM118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -10911,6 +11057,7 @@
       <c r="AJ119" t="inlineStr"/>
       <c r="AK119" t="inlineStr"/>
       <c r="AL119" t="inlineStr"/>
+      <c r="AM119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -10983,6 +11130,7 @@
       <c r="AJ120" t="inlineStr"/>
       <c r="AK120" t="inlineStr"/>
       <c r="AL120" t="inlineStr"/>
+      <c r="AM120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -11055,6 +11203,7 @@
       <c r="AJ121" t="inlineStr"/>
       <c r="AK121" t="inlineStr"/>
       <c r="AL121" t="inlineStr"/>
+      <c r="AM121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -11141,6 +11290,7 @@
       <c r="AJ122" t="inlineStr"/>
       <c r="AK122" t="inlineStr"/>
       <c r="AL122" t="inlineStr"/>
+      <c r="AM122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -11213,6 +11363,7 @@
       <c r="AJ123" t="inlineStr"/>
       <c r="AK123" t="inlineStr"/>
       <c r="AL123" t="inlineStr"/>
+      <c r="AM123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -11283,6 +11434,7 @@
       <c r="AJ124" t="inlineStr"/>
       <c r="AK124" t="inlineStr"/>
       <c r="AL124" t="inlineStr"/>
+      <c r="AM124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -11377,6 +11529,7 @@
       <c r="AJ125" t="inlineStr"/>
       <c r="AK125" t="inlineStr"/>
       <c r="AL125" t="inlineStr"/>
+      <c r="AM125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -11471,6 +11624,7 @@
       <c r="AJ126" t="inlineStr"/>
       <c r="AK126" t="inlineStr"/>
       <c r="AL126" t="inlineStr"/>
+      <c r="AM126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -11543,6 +11697,7 @@
       <c r="AJ127" t="inlineStr"/>
       <c r="AK127" t="inlineStr"/>
       <c r="AL127" t="inlineStr"/>
+      <c r="AM127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -11621,6 +11776,7 @@
       <c r="AJ128" t="inlineStr"/>
       <c r="AK128" t="inlineStr"/>
       <c r="AL128" t="inlineStr"/>
+      <c r="AM128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -11693,6 +11849,7 @@
       <c r="AJ129" t="inlineStr"/>
       <c r="AK129" t="inlineStr"/>
       <c r="AL129" t="inlineStr"/>
+      <c r="AM129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -11765,6 +11922,7 @@
       <c r="AJ130" t="inlineStr"/>
       <c r="AK130" t="inlineStr"/>
       <c r="AL130" t="inlineStr"/>
+      <c r="AM130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -11837,6 +11995,7 @@
       <c r="AJ131" t="inlineStr"/>
       <c r="AK131" t="inlineStr"/>
       <c r="AL131" t="inlineStr"/>
+      <c r="AM131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -11931,6 +12090,7 @@
       <c r="AJ132" t="inlineStr"/>
       <c r="AK132" t="inlineStr"/>
       <c r="AL132" t="inlineStr"/>
+      <c r="AM132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -12001,6 +12161,7 @@
       <c r="AJ133" t="inlineStr"/>
       <c r="AK133" t="inlineStr"/>
       <c r="AL133" t="inlineStr"/>
+      <c r="AM133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -12091,6 +12252,7 @@
       <c r="AJ134" t="inlineStr"/>
       <c r="AK134" t="inlineStr"/>
       <c r="AL134" t="inlineStr"/>
+      <c r="AM134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -12181,6 +12343,7 @@
       <c r="AJ135" t="inlineStr"/>
       <c r="AK135" t="inlineStr"/>
       <c r="AL135" t="inlineStr"/>
+      <c r="AM135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -12275,6 +12438,7 @@
       <c r="AJ136" t="inlineStr"/>
       <c r="AK136" t="inlineStr"/>
       <c r="AL136" t="inlineStr"/>
+      <c r="AM136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -12365,6 +12529,7 @@
       <c r="AJ137" t="inlineStr"/>
       <c r="AK137" t="inlineStr"/>
       <c r="AL137" t="inlineStr"/>
+      <c r="AM137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -12451,6 +12616,7 @@
       <c r="AJ138" t="inlineStr"/>
       <c r="AK138" t="inlineStr"/>
       <c r="AL138" t="inlineStr"/>
+      <c r="AM138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -12543,6 +12709,7 @@
       <c r="AJ139" t="inlineStr"/>
       <c r="AK139" t="inlineStr"/>
       <c r="AL139" t="inlineStr"/>
+      <c r="AM139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -12679,6 +12846,9 @@
         </is>
       </c>
       <c r="AL140" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM140" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12751,6 +12921,7 @@
       <c r="AJ141" t="inlineStr"/>
       <c r="AK141" t="inlineStr"/>
       <c r="AL141" t="inlineStr"/>
+      <c r="AM141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -12843,6 +13014,7 @@
       <c r="AJ142" t="inlineStr"/>
       <c r="AK142" t="inlineStr"/>
       <c r="AL142" t="inlineStr"/>
+      <c r="AM142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -12933,6 +13105,7 @@
       <c r="AJ143" t="inlineStr"/>
       <c r="AK143" t="inlineStr"/>
       <c r="AL143" t="inlineStr"/>
+      <c r="AM143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -13027,6 +13200,7 @@
       <c r="AJ144" t="inlineStr"/>
       <c r="AK144" t="inlineStr"/>
       <c r="AL144" t="inlineStr"/>
+      <c r="AM144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -13121,6 +13295,7 @@
       <c r="AJ145" t="inlineStr"/>
       <c r="AK145" t="inlineStr"/>
       <c r="AL145" t="inlineStr"/>
+      <c r="AM145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -13215,6 +13390,7 @@
       <c r="AJ146" t="inlineStr"/>
       <c r="AK146" t="inlineStr"/>
       <c r="AL146" t="inlineStr"/>
+      <c r="AM146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -13305,6 +13481,7 @@
       <c r="AJ147" t="inlineStr"/>
       <c r="AK147" t="inlineStr"/>
       <c r="AL147" t="inlineStr"/>
+      <c r="AM147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -13395,6 +13572,7 @@
       <c r="AJ148" t="inlineStr"/>
       <c r="AK148" t="inlineStr"/>
       <c r="AL148" t="inlineStr"/>
+      <c r="AM148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -13481,6 +13659,7 @@
       <c r="AJ149" t="inlineStr"/>
       <c r="AK149" t="inlineStr"/>
       <c r="AL149" t="inlineStr"/>
+      <c r="AM149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -13571,6 +13750,7 @@
       <c r="AJ150" t="inlineStr"/>
       <c r="AK150" t="inlineStr"/>
       <c r="AL150" t="inlineStr"/>
+      <c r="AM150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -13641,6 +13821,7 @@
       <c r="AJ151" t="inlineStr"/>
       <c r="AK151" t="inlineStr"/>
       <c r="AL151" t="inlineStr"/>
+      <c r="AM151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -13731,6 +13912,7 @@
       <c r="AJ152" t="inlineStr"/>
       <c r="AK152" t="inlineStr"/>
       <c r="AL152" t="inlineStr"/>
+      <c r="AM152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -13864,6 +14046,9 @@
       <c r="AK153" t="inlineStr"/>
       <c r="AL153" t="n">
         <v>1</v>
+      </c>
+      <c r="AM153" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="154">
@@ -13955,6 +14140,7 @@
       <c r="AJ154" t="inlineStr"/>
       <c r="AK154" t="inlineStr"/>
       <c r="AL154" t="inlineStr"/>
+      <c r="AM154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -14045,6 +14231,7 @@
       <c r="AJ155" t="inlineStr"/>
       <c r="AK155" t="inlineStr"/>
       <c r="AL155" t="inlineStr"/>
+      <c r="AM155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -14133,6 +14320,7 @@
       <c r="AJ156" t="inlineStr"/>
       <c r="AK156" t="inlineStr"/>
       <c r="AL156" t="inlineStr"/>
+      <c r="AM156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -14223,6 +14411,7 @@
       <c r="AJ157" t="inlineStr"/>
       <c r="AK157" t="inlineStr"/>
       <c r="AL157" t="inlineStr"/>
+      <c r="AM157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -14309,6 +14498,7 @@
       <c r="AJ158" t="inlineStr"/>
       <c r="AK158" t="inlineStr"/>
       <c r="AL158" t="inlineStr"/>
+      <c r="AM158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -14379,6 +14569,7 @@
       <c r="AJ159" t="inlineStr"/>
       <c r="AK159" t="inlineStr"/>
       <c r="AL159" t="inlineStr"/>
+      <c r="AM159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -14465,6 +14656,7 @@
       <c r="AJ160" t="inlineStr"/>
       <c r="AK160" t="inlineStr"/>
       <c r="AL160" t="inlineStr"/>
+      <c r="AM160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -14555,6 +14747,7 @@
       <c r="AJ161" t="inlineStr"/>
       <c r="AK161" t="inlineStr"/>
       <c r="AL161" t="inlineStr"/>
+      <c r="AM161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -14693,6 +14886,9 @@
       <c r="AL162" t="n">
         <v>1</v>
       </c>
+      <c r="AM162" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -14853,6 +15049,9 @@
         </is>
       </c>
       <c r="AL163" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM163" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14925,6 +15124,7 @@
       <c r="AJ164" t="inlineStr"/>
       <c r="AK164" t="inlineStr"/>
       <c r="AL164" t="inlineStr"/>
+      <c r="AM164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -14995,6 +15195,7 @@
       <c r="AJ165" t="inlineStr"/>
       <c r="AK165" t="inlineStr"/>
       <c r="AL165" t="inlineStr"/>
+      <c r="AM165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -15085,6 +15286,7 @@
       <c r="AJ166" t="inlineStr"/>
       <c r="AK166" t="inlineStr"/>
       <c r="AL166" t="inlineStr"/>
+      <c r="AM166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -15175,6 +15377,7 @@
       <c r="AJ167" t="inlineStr"/>
       <c r="AK167" t="inlineStr"/>
       <c r="AL167" t="inlineStr"/>
+      <c r="AM167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -15263,6 +15466,7 @@
       <c r="AJ168" t="inlineStr"/>
       <c r="AK168" t="inlineStr"/>
       <c r="AL168" t="inlineStr"/>
+      <c r="AM168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -15333,6 +15537,7 @@
       <c r="AJ169" t="inlineStr"/>
       <c r="AK169" t="inlineStr"/>
       <c r="AL169" t="inlineStr"/>
+      <c r="AM169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -15407,6 +15612,7 @@
       <c r="AJ170" t="inlineStr"/>
       <c r="AK170" t="inlineStr"/>
       <c r="AL170" t="inlineStr"/>
+      <c r="AM170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -15477,6 +15683,7 @@
       <c r="AJ171" t="inlineStr"/>
       <c r="AK171" t="inlineStr"/>
       <c r="AL171" t="inlineStr"/>
+      <c r="AM171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -15547,6 +15754,7 @@
       <c r="AJ172" t="inlineStr"/>
       <c r="AK172" t="inlineStr"/>
       <c r="AL172" t="inlineStr"/>
+      <c r="AM172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -15617,6 +15825,7 @@
       <c r="AJ173" t="inlineStr"/>
       <c r="AK173" t="inlineStr"/>
       <c r="AL173" t="inlineStr"/>
+      <c r="AM173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -15703,6 +15912,7 @@
       <c r="AJ174" t="inlineStr"/>
       <c r="AK174" t="inlineStr"/>
       <c r="AL174" t="inlineStr"/>
+      <c r="AM174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -15793,6 +16003,7 @@
       <c r="AJ175" t="inlineStr"/>
       <c r="AK175" t="inlineStr"/>
       <c r="AL175" t="inlineStr"/>
+      <c r="AM175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -15863,6 +16074,7 @@
       <c r="AJ176" t="inlineStr"/>
       <c r="AK176" t="inlineStr"/>
       <c r="AL176" t="inlineStr"/>
+      <c r="AM176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -15951,6 +16163,7 @@
       <c r="AJ177" t="inlineStr"/>
       <c r="AK177" t="inlineStr"/>
       <c r="AL177" t="inlineStr"/>
+      <c r="AM177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -16021,6 +16234,7 @@
       <c r="AJ178" t="inlineStr"/>
       <c r="AK178" t="inlineStr"/>
       <c r="AL178" t="inlineStr"/>
+      <c r="AM178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -16091,6 +16305,7 @@
       <c r="AJ179" t="inlineStr"/>
       <c r="AK179" t="inlineStr"/>
       <c r="AL179" t="inlineStr"/>
+      <c r="AM179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -16161,6 +16376,7 @@
       <c r="AJ180" t="inlineStr"/>
       <c r="AK180" t="inlineStr"/>
       <c r="AL180" t="inlineStr"/>
+      <c r="AM180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -16251,6 +16467,7 @@
       <c r="AJ181" t="inlineStr"/>
       <c r="AK181" t="inlineStr"/>
       <c r="AL181" t="inlineStr"/>
+      <c r="AM181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -16321,6 +16538,7 @@
       <c r="AJ182" t="inlineStr"/>
       <c r="AK182" t="inlineStr"/>
       <c r="AL182" t="inlineStr"/>
+      <c r="AM182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -16391,6 +16609,7 @@
       <c r="AJ183" t="inlineStr"/>
       <c r="AK183" t="inlineStr"/>
       <c r="AL183" t="inlineStr"/>
+      <c r="AM183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -16467,6 +16686,7 @@
       <c r="AJ184" t="inlineStr"/>
       <c r="AK184" t="inlineStr"/>
       <c r="AL184" t="inlineStr"/>
+      <c r="AM184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -16557,6 +16777,7 @@
       <c r="AJ185" t="inlineStr"/>
       <c r="AK185" t="inlineStr"/>
       <c r="AL185" t="inlineStr"/>
+      <c r="AM185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -16647,6 +16868,7 @@
       <c r="AJ186" t="inlineStr"/>
       <c r="AK186" t="inlineStr"/>
       <c r="AL186" t="inlineStr"/>
+      <c r="AM186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -16737,6 +16959,7 @@
       <c r="AJ187" t="inlineStr"/>
       <c r="AK187" t="inlineStr"/>
       <c r="AL187" t="inlineStr"/>
+      <c r="AM187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -16809,6 +17032,7 @@
       <c r="AJ188" t="inlineStr"/>
       <c r="AK188" t="inlineStr"/>
       <c r="AL188" t="inlineStr"/>
+      <c r="AM188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -16881,6 +17105,7 @@
       <c r="AJ189" t="inlineStr"/>
       <c r="AK189" t="inlineStr"/>
       <c r="AL189" t="inlineStr"/>
+      <c r="AM189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -16953,6 +17178,7 @@
       <c r="AJ190" t="inlineStr"/>
       <c r="AK190" t="inlineStr"/>
       <c r="AL190" t="inlineStr"/>
+      <c r="AM190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -17025,6 +17251,7 @@
       <c r="AJ191" t="inlineStr"/>
       <c r="AK191" t="inlineStr"/>
       <c r="AL191" t="inlineStr"/>
+      <c r="AM191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -17113,6 +17340,7 @@
       <c r="AJ192" t="inlineStr"/>
       <c r="AK192" t="inlineStr"/>
       <c r="AL192" t="inlineStr"/>
+      <c r="AM192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -17203,6 +17431,7 @@
       <c r="AJ193" t="inlineStr"/>
       <c r="AK193" t="inlineStr"/>
       <c r="AL193" t="inlineStr"/>
+      <c r="AM193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -17293,6 +17522,7 @@
       <c r="AJ194" t="inlineStr"/>
       <c r="AK194" t="inlineStr"/>
       <c r="AL194" t="inlineStr"/>
+      <c r="AM194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -17383,6 +17613,7 @@
       <c r="AJ195" t="inlineStr"/>
       <c r="AK195" t="inlineStr"/>
       <c r="AL195" t="inlineStr"/>
+      <c r="AM195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -17473,6 +17704,7 @@
       <c r="AJ196" t="inlineStr"/>
       <c r="AK196" t="inlineStr"/>
       <c r="AL196" t="inlineStr"/>
+      <c r="AM196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -17543,6 +17775,7 @@
       <c r="AJ197" t="inlineStr"/>
       <c r="AK197" t="inlineStr"/>
       <c r="AL197" t="inlineStr"/>
+      <c r="AM197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -17680,6 +17913,9 @@
       </c>
       <c r="AL198" t="n">
         <v>1</v>
+      </c>
+      <c r="AM198" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="199">
@@ -17751,6 +17987,7 @@
       <c r="AJ199" t="inlineStr"/>
       <c r="AK199" t="inlineStr"/>
       <c r="AL199" t="inlineStr"/>
+      <c r="AM199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -17821,6 +18058,7 @@
       <c r="AJ200" t="inlineStr"/>
       <c r="AK200" t="inlineStr"/>
       <c r="AL200" t="inlineStr"/>
+      <c r="AM200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -17891,6 +18129,7 @@
       <c r="AJ201" t="inlineStr"/>
       <c r="AK201" t="inlineStr"/>
       <c r="AL201" t="inlineStr"/>
+      <c r="AM201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -18027,6 +18266,9 @@
         </is>
       </c>
       <c r="AL202" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM202" t="n">
         <v>1</v>
       </c>
     </row>
@@ -18125,6 +18367,7 @@
       <c r="AJ203" t="inlineStr"/>
       <c r="AK203" t="inlineStr"/>
       <c r="AL203" t="inlineStr"/>
+      <c r="AM203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -18201,6 +18444,7 @@
       <c r="AJ204" t="inlineStr"/>
       <c r="AK204" t="inlineStr"/>
       <c r="AL204" t="inlineStr"/>
+      <c r="AM204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -18275,6 +18519,7 @@
       <c r="AJ205" t="inlineStr"/>
       <c r="AK205" t="inlineStr"/>
       <c r="AL205" t="inlineStr"/>
+      <c r="AM205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -18363,6 +18608,7 @@
       <c r="AJ206" t="inlineStr"/>
       <c r="AK206" t="inlineStr"/>
       <c r="AL206" t="inlineStr"/>
+      <c r="AM206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -18499,6 +18745,9 @@
         </is>
       </c>
       <c r="AL207" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM207" t="n">
         <v>1</v>
       </c>
     </row>
@@ -18571,6 +18820,7 @@
       <c r="AJ208" t="inlineStr"/>
       <c r="AK208" t="inlineStr"/>
       <c r="AL208" t="inlineStr"/>
+      <c r="AM208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -18667,6 +18917,7 @@
       <c r="AJ209" t="inlineStr"/>
       <c r="AK209" t="inlineStr"/>
       <c r="AL209" t="inlineStr"/>
+      <c r="AM209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -18753,6 +19004,7 @@
       <c r="AJ210" t="inlineStr"/>
       <c r="AK210" t="inlineStr"/>
       <c r="AL210" t="inlineStr"/>
+      <c r="AM210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -18841,6 +19093,7 @@
       <c r="AJ211" t="inlineStr"/>
       <c r="AK211" t="inlineStr"/>
       <c r="AL211" t="inlineStr"/>
+      <c r="AM211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -18927,6 +19180,7 @@
       <c r="AJ212" t="inlineStr"/>
       <c r="AK212" t="inlineStr"/>
       <c r="AL212" t="inlineStr"/>
+      <c r="AM212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -19015,6 +19269,7 @@
       <c r="AJ213" t="inlineStr"/>
       <c r="AK213" t="inlineStr"/>
       <c r="AL213" t="inlineStr"/>
+      <c r="AM213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -19089,6 +19344,7 @@
       <c r="AJ214" t="inlineStr"/>
       <c r="AK214" t="inlineStr"/>
       <c r="AL214" t="inlineStr"/>
+      <c r="AM214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -19175,6 +19431,7 @@
       <c r="AJ215" t="inlineStr"/>
       <c r="AK215" t="inlineStr"/>
       <c r="AL215" t="inlineStr"/>
+      <c r="AM215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -19261,6 +19518,7 @@
       <c r="AJ216" t="inlineStr"/>
       <c r="AK216" t="inlineStr"/>
       <c r="AL216" t="inlineStr"/>
+      <c r="AM216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -19347,6 +19605,7 @@
       <c r="AJ217" t="inlineStr"/>
       <c r="AK217" t="inlineStr"/>
       <c r="AL217" t="inlineStr"/>
+      <c r="AM217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -19417,6 +19676,7 @@
       <c r="AJ218" t="inlineStr"/>
       <c r="AK218" t="inlineStr"/>
       <c r="AL218" t="inlineStr"/>
+      <c r="AM218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -19487,6 +19747,7 @@
       <c r="AJ219" t="inlineStr"/>
       <c r="AK219" t="inlineStr"/>
       <c r="AL219" t="inlineStr"/>
+      <c r="AM219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -19621,6 +19882,9 @@
       <c r="AL220" t="n">
         <v>1</v>
       </c>
+      <c r="AM220" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -19754,6 +20018,9 @@
       <c r="AK221" t="inlineStr"/>
       <c r="AL221" t="n">
         <v>1</v>
+      </c>
+      <c r="AM221" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="222">
@@ -19825,6 +20092,7 @@
       <c r="AJ222" t="inlineStr"/>
       <c r="AK222" t="inlineStr"/>
       <c r="AL222" t="inlineStr"/>
+      <c r="AM222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -19899,6 +20167,7 @@
       <c r="AJ223" t="inlineStr"/>
       <c r="AK223" t="inlineStr"/>
       <c r="AL223" t="inlineStr"/>
+      <c r="AM223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -19969,6 +20238,7 @@
       <c r="AJ224" t="inlineStr"/>
       <c r="AK224" t="inlineStr"/>
       <c r="AL224" t="inlineStr"/>
+      <c r="AM224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -20039,6 +20309,7 @@
       <c r="AJ225" t="inlineStr"/>
       <c r="AK225" t="inlineStr"/>
       <c r="AL225" t="inlineStr"/>
+      <c r="AM225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -20109,6 +20380,7 @@
       <c r="AJ226" t="inlineStr"/>
       <c r="AK226" t="inlineStr"/>
       <c r="AL226" t="inlineStr"/>
+      <c r="AM226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -20179,6 +20451,7 @@
       <c r="AJ227" t="inlineStr"/>
       <c r="AK227" t="inlineStr"/>
       <c r="AL227" t="inlineStr"/>
+      <c r="AM227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -20265,6 +20538,7 @@
       <c r="AJ228" t="inlineStr"/>
       <c r="AK228" t="inlineStr"/>
       <c r="AL228" t="inlineStr"/>
+      <c r="AM228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -20335,6 +20609,7 @@
       <c r="AJ229" t="inlineStr"/>
       <c r="AK229" t="inlineStr"/>
       <c r="AL229" t="inlineStr"/>
+      <c r="AM229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -20405,6 +20680,7 @@
       <c r="AJ230" t="inlineStr"/>
       <c r="AK230" t="inlineStr"/>
       <c r="AL230" t="inlineStr"/>
+      <c r="AM230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -20479,6 +20755,7 @@
       <c r="AJ231" t="inlineStr"/>
       <c r="AK231" t="inlineStr"/>
       <c r="AL231" t="inlineStr"/>
+      <c r="AM231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -20551,6 +20828,7 @@
       <c r="AJ232" t="inlineStr"/>
       <c r="AK232" t="inlineStr"/>
       <c r="AL232" t="inlineStr"/>
+      <c r="AM232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -20623,6 +20901,7 @@
       <c r="AJ233" t="inlineStr"/>
       <c r="AK233" t="inlineStr"/>
       <c r="AL233" t="inlineStr"/>
+      <c r="AM233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -20760,6 +21039,9 @@
       </c>
       <c r="AL234" t="n">
         <v>1</v>
+      </c>
+      <c r="AM234" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="235">
@@ -20831,6 +21113,7 @@
       <c r="AJ235" t="inlineStr"/>
       <c r="AK235" t="inlineStr"/>
       <c r="AL235" t="inlineStr"/>
+      <c r="AM235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -20903,6 +21186,7 @@
       <c r="AJ236" t="inlineStr"/>
       <c r="AK236" t="inlineStr"/>
       <c r="AL236" t="inlineStr"/>
+      <c r="AM236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -20981,6 +21265,7 @@
       <c r="AJ237" t="inlineStr"/>
       <c r="AK237" t="inlineStr"/>
       <c r="AL237" t="inlineStr"/>
+      <c r="AM237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -21075,6 +21360,7 @@
       <c r="AJ238" t="inlineStr"/>
       <c r="AK238" t="inlineStr"/>
       <c r="AL238" t="inlineStr"/>
+      <c r="AM238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -21145,6 +21431,7 @@
       <c r="AJ239" t="inlineStr"/>
       <c r="AK239" t="inlineStr"/>
       <c r="AL239" t="inlineStr"/>
+      <c r="AM239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -21215,6 +21502,7 @@
       <c r="AJ240" t="inlineStr"/>
       <c r="AK240" t="inlineStr"/>
       <c r="AL240" t="inlineStr"/>
+      <c r="AM240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -21353,6 +21641,9 @@
       <c r="AL241" t="n">
         <v>1</v>
       </c>
+      <c r="AM241" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -21498,6 +21789,9 @@
       </c>
       <c r="AL242" t="n">
         <v>1</v>
+      </c>
+      <c r="AM242" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="243">
@@ -21569,6 +21863,7 @@
       <c r="AJ243" t="inlineStr"/>
       <c r="AK243" t="inlineStr"/>
       <c r="AL243" t="inlineStr"/>
+      <c r="AM243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -21639,6 +21934,7 @@
       <c r="AJ244" t="inlineStr"/>
       <c r="AK244" t="inlineStr"/>
       <c r="AL244" t="inlineStr"/>
+      <c r="AM244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -21711,6 +22007,7 @@
       <c r="AJ245" t="inlineStr"/>
       <c r="AK245" t="inlineStr"/>
       <c r="AL245" t="inlineStr"/>
+      <c r="AM245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -21781,6 +22078,7 @@
       <c r="AJ246" t="inlineStr"/>
       <c r="AK246" t="inlineStr"/>
       <c r="AL246" t="inlineStr"/>
+      <c r="AM246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -21851,6 +22149,7 @@
       <c r="AJ247" t="inlineStr"/>
       <c r="AK247" t="inlineStr"/>
       <c r="AL247" t="inlineStr"/>
+      <c r="AM247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -21921,6 +22220,7 @@
       <c r="AJ248" t="inlineStr"/>
       <c r="AK248" t="inlineStr"/>
       <c r="AL248" t="inlineStr"/>
+      <c r="AM248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -21991,6 +22291,7 @@
       <c r="AJ249" t="inlineStr"/>
       <c r="AK249" t="inlineStr"/>
       <c r="AL249" t="inlineStr"/>
+      <c r="AM249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -22061,6 +22362,7 @@
       <c r="AJ250" t="inlineStr"/>
       <c r="AK250" t="inlineStr"/>
       <c r="AL250" t="inlineStr"/>
+      <c r="AM250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -22131,6 +22433,7 @@
       <c r="AJ251" t="inlineStr"/>
       <c r="AK251" t="inlineStr"/>
       <c r="AL251" t="inlineStr"/>
+      <c r="AM251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -22201,6 +22504,7 @@
       <c r="AJ252" t="inlineStr"/>
       <c r="AK252" t="inlineStr"/>
       <c r="AL252" t="inlineStr"/>
+      <c r="AM252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -22338,6 +22642,9 @@
       </c>
       <c r="AL253" t="n">
         <v>1</v>
+      </c>
+      <c r="AM253" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="254">
@@ -22409,6 +22716,7 @@
       <c r="AJ254" t="inlineStr"/>
       <c r="AK254" t="inlineStr"/>
       <c r="AL254" t="inlineStr"/>
+      <c r="AM254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -22479,6 +22787,7 @@
       <c r="AJ255" t="inlineStr"/>
       <c r="AK255" t="inlineStr"/>
       <c r="AL255" t="inlineStr"/>
+      <c r="AM255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -22549,6 +22858,7 @@
       <c r="AJ256" t="inlineStr"/>
       <c r="AK256" t="inlineStr"/>
       <c r="AL256" t="inlineStr"/>
+      <c r="AM256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -22619,6 +22929,7 @@
       <c r="AJ257" t="inlineStr"/>
       <c r="AK257" t="inlineStr"/>
       <c r="AL257" t="inlineStr"/>
+      <c r="AM257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -22689,6 +23000,7 @@
       <c r="AJ258" t="inlineStr"/>
       <c r="AK258" t="inlineStr"/>
       <c r="AL258" t="inlineStr"/>
+      <c r="AM258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -22825,6 +23137,9 @@
         </is>
       </c>
       <c r="AL259" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM259" t="n">
         <v>1</v>
       </c>
     </row>
@@ -22913,6 +23228,7 @@
       <c r="AJ260" t="inlineStr"/>
       <c r="AK260" t="inlineStr"/>
       <c r="AL260" t="inlineStr"/>
+      <c r="AM260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -22987,6 +23303,7 @@
       <c r="AJ261" t="inlineStr"/>
       <c r="AK261" t="inlineStr"/>
       <c r="AL261" t="inlineStr"/>
+      <c r="AM261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -23077,6 +23394,7 @@
       <c r="AJ262" t="inlineStr"/>
       <c r="AK262" t="inlineStr"/>
       <c r="AL262" t="inlineStr"/>
+      <c r="AM262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -23147,6 +23465,7 @@
       <c r="AJ263" t="inlineStr"/>
       <c r="AK263" t="inlineStr"/>
       <c r="AL263" t="inlineStr"/>
+      <c r="AM263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -23217,6 +23536,7 @@
       <c r="AJ264" t="inlineStr"/>
       <c r="AK264" t="inlineStr"/>
       <c r="AL264" t="inlineStr"/>
+      <c r="AM264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -23305,6 +23625,7 @@
       <c r="AJ265" t="inlineStr"/>
       <c r="AK265" t="inlineStr"/>
       <c r="AL265" t="inlineStr"/>
+      <c r="AM265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -23379,6 +23700,7 @@
       <c r="AJ266" t="inlineStr"/>
       <c r="AK266" t="inlineStr"/>
       <c r="AL266" t="inlineStr"/>
+      <c r="AM266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -23449,6 +23771,7 @@
       <c r="AJ267" t="inlineStr"/>
       <c r="AK267" t="inlineStr"/>
       <c r="AL267" t="inlineStr"/>
+      <c r="AM267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -23519,6 +23842,7 @@
       <c r="AJ268" t="inlineStr"/>
       <c r="AK268" t="inlineStr"/>
       <c r="AL268" t="inlineStr"/>
+      <c r="AM268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -23613,6 +23937,7 @@
       <c r="AJ269" t="inlineStr"/>
       <c r="AK269" t="inlineStr"/>
       <c r="AL269" t="inlineStr"/>
+      <c r="AM269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -23707,6 +24032,7 @@
       <c r="AJ270" t="inlineStr"/>
       <c r="AK270" t="inlineStr"/>
       <c r="AL270" t="inlineStr"/>
+      <c r="AM270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -23783,6 +24109,7 @@
       <c r="AJ271" t="inlineStr"/>
       <c r="AK271" t="inlineStr"/>
       <c r="AL271" t="inlineStr"/>
+      <c r="AM271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -23865,6 +24192,7 @@
       <c r="AJ272" t="inlineStr"/>
       <c r="AK272" t="inlineStr"/>
       <c r="AL272" t="inlineStr"/>
+      <c r="AM272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -23935,6 +24263,7 @@
       <c r="AJ273" t="inlineStr"/>
       <c r="AK273" t="inlineStr"/>
       <c r="AL273" t="inlineStr"/>
+      <c r="AM273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -24009,6 +24338,7 @@
       <c r="AJ274" t="inlineStr"/>
       <c r="AK274" t="inlineStr"/>
       <c r="AL274" t="inlineStr"/>
+      <c r="AM274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -24079,6 +24409,7 @@
       <c r="AJ275" t="inlineStr"/>
       <c r="AK275" t="inlineStr"/>
       <c r="AL275" t="inlineStr"/>
+      <c r="AM275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -24175,6 +24506,7 @@
       <c r="AJ276" t="inlineStr"/>
       <c r="AK276" t="inlineStr"/>
       <c r="AL276" t="inlineStr"/>
+      <c r="AM276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -24261,6 +24593,7 @@
       <c r="AJ277" t="inlineStr"/>
       <c r="AK277" t="inlineStr"/>
       <c r="AL277" t="inlineStr"/>
+      <c r="AM277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -24333,6 +24666,7 @@
       <c r="AJ278" t="inlineStr"/>
       <c r="AK278" t="inlineStr"/>
       <c r="AL278" t="inlineStr"/>
+      <c r="AM278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -24403,6 +24737,7 @@
       <c r="AJ279" t="inlineStr"/>
       <c r="AK279" t="inlineStr"/>
       <c r="AL279" t="inlineStr"/>
+      <c r="AM279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -24473,6 +24808,7 @@
       <c r="AJ280" t="inlineStr"/>
       <c r="AK280" t="inlineStr"/>
       <c r="AL280" t="inlineStr"/>
+      <c r="AM280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -24563,6 +24899,7 @@
       <c r="AJ281" t="inlineStr"/>
       <c r="AK281" t="inlineStr"/>
       <c r="AL281" t="inlineStr"/>
+      <c r="AM281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -24653,6 +24990,7 @@
       <c r="AJ282" t="inlineStr"/>
       <c r="AK282" t="inlineStr"/>
       <c r="AL282" t="inlineStr"/>
+      <c r="AM282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -24725,6 +25063,7 @@
       <c r="AJ283" t="inlineStr"/>
       <c r="AK283" t="inlineStr"/>
       <c r="AL283" t="inlineStr"/>
+      <c r="AM283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -24811,6 +25150,7 @@
       <c r="AJ284" t="inlineStr"/>
       <c r="AK284" t="inlineStr"/>
       <c r="AL284" t="inlineStr"/>
+      <c r="AM284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -24881,6 +25221,7 @@
       <c r="AJ285" t="inlineStr"/>
       <c r="AK285" t="inlineStr"/>
       <c r="AL285" t="inlineStr"/>
+      <c r="AM285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -24969,6 +25310,7 @@
       <c r="AJ286" t="inlineStr"/>
       <c r="AK286" t="inlineStr"/>
       <c r="AL286" t="inlineStr"/>
+      <c r="AM286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -25041,6 +25383,7 @@
       <c r="AJ287" t="inlineStr"/>
       <c r="AK287" t="inlineStr"/>
       <c r="AL287" t="inlineStr"/>
+      <c r="AM287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -25113,6 +25456,7 @@
       <c r="AJ288" t="inlineStr"/>
       <c r="AK288" t="inlineStr"/>
       <c r="AL288" t="inlineStr"/>
+      <c r="AM288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -25274,6 +25618,9 @@
       </c>
       <c r="AL289" t="n">
         <v>1</v>
+      </c>
+      <c r="AM289" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="290">
@@ -25347,6 +25694,7 @@
       <c r="AJ290" t="inlineStr"/>
       <c r="AK290" t="inlineStr"/>
       <c r="AL290" t="inlineStr"/>
+      <c r="AM290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -25435,6 +25783,7 @@
       <c r="AJ291" t="inlineStr"/>
       <c r="AK291" t="inlineStr"/>
       <c r="AL291" t="inlineStr"/>
+      <c r="AM291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -25507,6 +25856,7 @@
       <c r="AJ292" t="inlineStr"/>
       <c r="AK292" t="inlineStr"/>
       <c r="AL292" t="inlineStr"/>
+      <c r="AM292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -25577,6 +25927,7 @@
       <c r="AJ293" t="inlineStr"/>
       <c r="AK293" t="inlineStr"/>
       <c r="AL293" t="inlineStr"/>
+      <c r="AM293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -25715,6 +26066,9 @@
       <c r="AL294" t="n">
         <v>1</v>
       </c>
+      <c r="AM294" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -25851,6 +26205,9 @@
         </is>
       </c>
       <c r="AL295" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM295" t="n">
         <v>1</v>
       </c>
     </row>
@@ -25923,6 +26280,7 @@
       <c r="AJ296" t="inlineStr"/>
       <c r="AK296" t="inlineStr"/>
       <c r="AL296" t="inlineStr"/>
+      <c r="AM296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -26055,6 +26413,9 @@
         </is>
       </c>
       <c r="AL297" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM297" t="n">
         <v>1</v>
       </c>
     </row>
@@ -26147,6 +26508,7 @@
       <c r="AJ298" t="inlineStr"/>
       <c r="AK298" t="inlineStr"/>
       <c r="AL298" t="inlineStr"/>
+      <c r="AM298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -26217,6 +26579,7 @@
       <c r="AJ299" t="inlineStr"/>
       <c r="AK299" t="inlineStr"/>
       <c r="AL299" t="inlineStr"/>
+      <c r="AM299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -26307,6 +26670,7 @@
       <c r="AJ300" t="inlineStr"/>
       <c r="AK300" t="inlineStr"/>
       <c r="AL300" t="inlineStr"/>
+      <c r="AM300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -26379,6 +26743,7 @@
       <c r="AJ301" t="inlineStr"/>
       <c r="AK301" t="inlineStr"/>
       <c r="AL301" t="inlineStr"/>
+      <c r="AM301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -26451,6 +26816,7 @@
       <c r="AJ302" t="inlineStr"/>
       <c r="AK302" t="inlineStr"/>
       <c r="AL302" t="inlineStr"/>
+      <c r="AM302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -26523,6 +26889,7 @@
       <c r="AJ303" t="inlineStr"/>
       <c r="AK303" t="inlineStr"/>
       <c r="AL303" t="inlineStr"/>
+      <c r="AM303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -26659,6 +27026,9 @@
         </is>
       </c>
       <c r="AL304" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM304" t="n">
         <v>1</v>
       </c>
     </row>
@@ -26733,6 +27103,7 @@
       <c r="AJ305" t="inlineStr"/>
       <c r="AK305" t="inlineStr"/>
       <c r="AL305" t="inlineStr"/>
+      <c r="AM305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -26803,6 +27174,7 @@
       <c r="AJ306" t="inlineStr"/>
       <c r="AK306" t="inlineStr"/>
       <c r="AL306" t="inlineStr"/>
+      <c r="AM306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -26935,6 +27307,9 @@
       </c>
       <c r="AK307" t="inlineStr"/>
       <c r="AL307" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM307" t="n">
         <v>1</v>
       </c>
     </row>
@@ -27007,6 +27382,7 @@
       <c r="AJ308" t="inlineStr"/>
       <c r="AK308" t="inlineStr"/>
       <c r="AL308" t="inlineStr"/>
+      <c r="AM308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -27077,6 +27453,7 @@
       <c r="AJ309" t="inlineStr"/>
       <c r="AK309" t="inlineStr"/>
       <c r="AL309" t="inlineStr"/>
+      <c r="AM309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -27147,6 +27524,7 @@
       <c r="AJ310" t="inlineStr"/>
       <c r="AK310" t="inlineStr"/>
       <c r="AL310" t="inlineStr"/>
+      <c r="AM310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -27284,6 +27662,9 @@
       </c>
       <c r="AL311" t="n">
         <v>1</v>
+      </c>
+      <c r="AM311" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="312">
@@ -27355,6 +27736,7 @@
       <c r="AJ312" t="inlineStr"/>
       <c r="AK312" t="inlineStr"/>
       <c r="AL312" t="inlineStr"/>
+      <c r="AM312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -27427,6 +27809,7 @@
       <c r="AJ313" t="inlineStr"/>
       <c r="AK313" t="inlineStr"/>
       <c r="AL313" t="inlineStr"/>
+      <c r="AM313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -27563,6 +27946,9 @@
         </is>
       </c>
       <c r="AL314" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM314" t="n">
         <v>1</v>
       </c>
     </row>
@@ -27635,6 +28021,7 @@
       <c r="AJ315" t="inlineStr"/>
       <c r="AK315" t="inlineStr"/>
       <c r="AL315" t="inlineStr"/>
+      <c r="AM315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -27729,6 +28116,7 @@
       <c r="AJ316" t="inlineStr"/>
       <c r="AK316" t="inlineStr"/>
       <c r="AL316" t="inlineStr"/>
+      <c r="AM316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -27819,6 +28207,7 @@
       <c r="AJ317" t="inlineStr"/>
       <c r="AK317" t="inlineStr"/>
       <c r="AL317" t="inlineStr"/>
+      <c r="AM317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -27905,6 +28294,7 @@
       <c r="AJ318" t="inlineStr"/>
       <c r="AK318" t="inlineStr"/>
       <c r="AL318" t="inlineStr"/>
+      <c r="AM318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -27991,6 +28381,7 @@
       <c r="AJ319" t="inlineStr"/>
       <c r="AK319" t="inlineStr"/>
       <c r="AL319" t="inlineStr"/>
+      <c r="AM319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -28061,6 +28452,7 @@
       <c r="AJ320" t="inlineStr"/>
       <c r="AK320" t="inlineStr"/>
       <c r="AL320" t="inlineStr"/>
+      <c r="AM320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -28135,6 +28527,7 @@
       <c r="AJ321" t="inlineStr"/>
       <c r="AK321" t="inlineStr"/>
       <c r="AL321" t="inlineStr"/>
+      <c r="AM321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -28205,6 +28598,7 @@
       <c r="AJ322" t="inlineStr"/>
       <c r="AK322" t="inlineStr"/>
       <c r="AL322" t="inlineStr"/>
+      <c r="AM322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -28275,6 +28669,7 @@
       <c r="AJ323" t="inlineStr"/>
       <c r="AK323" t="inlineStr"/>
       <c r="AL323" t="inlineStr"/>
+      <c r="AM323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -28345,6 +28740,7 @@
       <c r="AJ324" t="inlineStr"/>
       <c r="AK324" t="inlineStr"/>
       <c r="AL324" t="inlineStr"/>
+      <c r="AM324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -28415,6 +28811,7 @@
       <c r="AJ325" t="inlineStr"/>
       <c r="AK325" t="inlineStr"/>
       <c r="AL325" t="inlineStr"/>
+      <c r="AM325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -28503,6 +28900,7 @@
       <c r="AJ326" t="inlineStr"/>
       <c r="AK326" t="inlineStr"/>
       <c r="AL326" t="inlineStr"/>
+      <c r="AM326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -28597,6 +28995,7 @@
       <c r="AJ327" t="inlineStr"/>
       <c r="AK327" t="inlineStr"/>
       <c r="AL327" t="inlineStr"/>
+      <c r="AM327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -28691,6 +29090,7 @@
       <c r="AJ328" t="inlineStr"/>
       <c r="AK328" t="inlineStr"/>
       <c r="AL328" t="inlineStr"/>
+      <c r="AM328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -28761,6 +29161,7 @@
       <c r="AJ329" t="inlineStr"/>
       <c r="AK329" t="inlineStr"/>
       <c r="AL329" t="inlineStr"/>
+      <c r="AM329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -28851,6 +29252,7 @@
       <c r="AJ330" t="inlineStr"/>
       <c r="AK330" t="inlineStr"/>
       <c r="AL330" t="inlineStr"/>
+      <c r="AM330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -28937,6 +29339,7 @@
       <c r="AJ331" t="inlineStr"/>
       <c r="AK331" t="inlineStr"/>
       <c r="AL331" t="inlineStr"/>
+      <c r="AM331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -29027,6 +29430,7 @@
       <c r="AJ332" t="inlineStr"/>
       <c r="AK332" t="inlineStr"/>
       <c r="AL332" t="inlineStr"/>
+      <c r="AM332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -29097,6 +29501,7 @@
       <c r="AJ333" t="inlineStr"/>
       <c r="AK333" t="inlineStr"/>
       <c r="AL333" t="inlineStr"/>
+      <c r="AM333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -29185,6 +29590,7 @@
       <c r="AJ334" t="inlineStr"/>
       <c r="AK334" t="inlineStr"/>
       <c r="AL334" t="inlineStr"/>
+      <c r="AM334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -29275,6 +29681,7 @@
       <c r="AJ335" t="inlineStr"/>
       <c r="AK335" t="inlineStr"/>
       <c r="AL335" t="inlineStr"/>
+      <c r="AM335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -29371,6 +29778,7 @@
       <c r="AJ336" t="inlineStr"/>
       <c r="AK336" t="inlineStr"/>
       <c r="AL336" t="inlineStr"/>
+      <c r="AM336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -29441,6 +29849,7 @@
       <c r="AJ337" t="inlineStr"/>
       <c r="AK337" t="inlineStr"/>
       <c r="AL337" t="inlineStr"/>
+      <c r="AM337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -29511,6 +29920,7 @@
       <c r="AJ338" t="inlineStr"/>
       <c r="AK338" t="inlineStr"/>
       <c r="AL338" t="inlineStr"/>
+      <c r="AM338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -29599,6 +30009,7 @@
       <c r="AJ339" t="inlineStr"/>
       <c r="AK339" t="inlineStr"/>
       <c r="AL339" t="inlineStr"/>
+      <c r="AM339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -29669,6 +30080,7 @@
       <c r="AJ340" t="inlineStr"/>
       <c r="AK340" t="inlineStr"/>
       <c r="AL340" t="inlineStr"/>
+      <c r="AM340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -29739,6 +30151,7 @@
       <c r="AJ341" t="inlineStr"/>
       <c r="AK341" t="inlineStr"/>
       <c r="AL341" t="inlineStr"/>
+      <c r="AM341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -29825,6 +30238,7 @@
       <c r="AJ342" t="inlineStr"/>
       <c r="AK342" t="inlineStr"/>
       <c r="AL342" t="inlineStr"/>
+      <c r="AM342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -29919,6 +30333,7 @@
       <c r="AJ343" t="inlineStr"/>
       <c r="AK343" t="inlineStr"/>
       <c r="AL343" t="inlineStr"/>
+      <c r="AM343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -30055,6 +30470,9 @@
         </is>
       </c>
       <c r="AL344" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM344" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30127,6 +30545,7 @@
       <c r="AJ345" t="inlineStr"/>
       <c r="AK345" t="inlineStr"/>
       <c r="AL345" t="inlineStr"/>
+      <c r="AM345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -30197,6 +30616,7 @@
       <c r="AJ346" t="inlineStr"/>
       <c r="AK346" t="inlineStr"/>
       <c r="AL346" t="inlineStr"/>
+      <c r="AM346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -30291,6 +30711,7 @@
       <c r="AJ347" t="inlineStr"/>
       <c r="AK347" t="inlineStr"/>
       <c r="AL347" t="inlineStr"/>
+      <c r="AM347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -30381,6 +30802,7 @@
       <c r="AJ348" t="inlineStr"/>
       <c r="AK348" t="inlineStr"/>
       <c r="AL348" t="inlineStr"/>
+      <c r="AM348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -30471,6 +30893,7 @@
       <c r="AJ349" t="inlineStr"/>
       <c r="AK349" t="inlineStr"/>
       <c r="AL349" t="inlineStr"/>
+      <c r="AM349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -30567,6 +30990,7 @@
       <c r="AJ350" t="inlineStr"/>
       <c r="AK350" t="inlineStr"/>
       <c r="AL350" t="inlineStr"/>
+      <c r="AM350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -30727,6 +31151,9 @@
         </is>
       </c>
       <c r="AL351" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM351" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30799,6 +31226,7 @@
       <c r="AJ352" t="inlineStr"/>
       <c r="AK352" t="inlineStr"/>
       <c r="AL352" t="inlineStr"/>
+      <c r="AM352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -30869,6 +31297,7 @@
       <c r="AJ353" t="inlineStr"/>
       <c r="AK353" t="inlineStr"/>
       <c r="AL353" t="inlineStr"/>
+      <c r="AM353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -30957,6 +31386,7 @@
       <c r="AJ354" t="inlineStr"/>
       <c r="AK354" t="inlineStr"/>
       <c r="AL354" t="inlineStr"/>
+      <c r="AM354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -31031,6 +31461,7 @@
       <c r="AJ355" t="inlineStr"/>
       <c r="AK355" t="inlineStr"/>
       <c r="AL355" t="inlineStr"/>
+      <c r="AM355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -31101,6 +31532,7 @@
       <c r="AJ356" t="inlineStr"/>
       <c r="AK356" t="inlineStr"/>
       <c r="AL356" t="inlineStr"/>
+      <c r="AM356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -31171,6 +31603,7 @@
       <c r="AJ357" t="inlineStr"/>
       <c r="AK357" t="inlineStr"/>
       <c r="AL357" t="inlineStr"/>
+      <c r="AM357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -31259,6 +31692,7 @@
       <c r="AJ358" t="inlineStr"/>
       <c r="AK358" t="inlineStr"/>
       <c r="AL358" t="inlineStr"/>
+      <c r="AM358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -31329,6 +31763,7 @@
       <c r="AJ359" t="inlineStr"/>
       <c r="AK359" t="inlineStr"/>
       <c r="AL359" t="inlineStr"/>
+      <c r="AM359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -31425,6 +31860,7 @@
       <c r="AJ360" t="inlineStr"/>
       <c r="AK360" t="inlineStr"/>
       <c r="AL360" t="inlineStr"/>
+      <c r="AM360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -31521,6 +31957,7 @@
       <c r="AJ361" t="inlineStr"/>
       <c r="AK361" t="inlineStr"/>
       <c r="AL361" t="inlineStr"/>
+      <c r="AM361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -31591,6 +32028,7 @@
       <c r="AJ362" t="inlineStr"/>
       <c r="AK362" t="inlineStr"/>
       <c r="AL362" t="inlineStr"/>
+      <c r="AM362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -31681,6 +32119,7 @@
       <c r="AJ363" t="inlineStr"/>
       <c r="AK363" t="inlineStr"/>
       <c r="AL363" t="inlineStr"/>
+      <c r="AM363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -31777,6 +32216,7 @@
       <c r="AJ364" t="inlineStr"/>
       <c r="AK364" t="inlineStr"/>
       <c r="AL364" t="inlineStr"/>
+      <c r="AM364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -31853,6 +32293,7 @@
       <c r="AJ365" t="inlineStr"/>
       <c r="AK365" t="inlineStr"/>
       <c r="AL365" t="inlineStr"/>
+      <c r="AM365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -31949,6 +32390,7 @@
       <c r="AJ366" t="inlineStr"/>
       <c r="AK366" t="inlineStr"/>
       <c r="AL366" t="inlineStr"/>
+      <c r="AM366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -32035,6 +32477,7 @@
       <c r="AJ367" t="inlineStr"/>
       <c r="AK367" t="inlineStr"/>
       <c r="AL367" t="inlineStr"/>
+      <c r="AM367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -32105,6 +32548,7 @@
       <c r="AJ368" t="inlineStr"/>
       <c r="AK368" t="inlineStr"/>
       <c r="AL368" t="inlineStr"/>
+      <c r="AM368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -32195,6 +32639,7 @@
       <c r="AJ369" t="inlineStr"/>
       <c r="AK369" t="inlineStr"/>
       <c r="AL369" t="inlineStr"/>
+      <c r="AM369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -32291,6 +32736,7 @@
       <c r="AJ370" t="inlineStr"/>
       <c r="AK370" t="inlineStr"/>
       <c r="AL370" t="inlineStr"/>
+      <c r="AM370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -32365,6 +32811,7 @@
       <c r="AJ371" t="inlineStr"/>
       <c r="AK371" t="inlineStr"/>
       <c r="AL371" t="inlineStr"/>
+      <c r="AM371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -32453,6 +32900,7 @@
       <c r="AJ372" t="inlineStr"/>
       <c r="AK372" t="inlineStr"/>
       <c r="AL372" t="inlineStr"/>
+      <c r="AM372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -32523,6 +32971,7 @@
       <c r="AJ373" t="inlineStr"/>
       <c r="AK373" t="inlineStr"/>
       <c r="AL373" t="inlineStr"/>
+      <c r="AM373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -32593,6 +33042,7 @@
       <c r="AJ374" t="inlineStr"/>
       <c r="AK374" t="inlineStr"/>
       <c r="AL374" t="inlineStr"/>
+      <c r="AM374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -32683,6 +33133,7 @@
       <c r="AJ375" t="inlineStr"/>
       <c r="AK375" t="inlineStr"/>
       <c r="AL375" t="inlineStr"/>
+      <c r="AM375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -32771,6 +33222,7 @@
       <c r="AJ376" t="inlineStr"/>
       <c r="AK376" t="inlineStr"/>
       <c r="AL376" t="inlineStr"/>
+      <c r="AM376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -32841,6 +33293,7 @@
       <c r="AJ377" t="inlineStr"/>
       <c r="AK377" t="inlineStr"/>
       <c r="AL377" t="inlineStr"/>
+      <c r="AM377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -32911,6 +33364,7 @@
       <c r="AJ378" t="inlineStr"/>
       <c r="AK378" t="inlineStr"/>
       <c r="AL378" t="inlineStr"/>
+      <c r="AM378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -32997,6 +33451,7 @@
       <c r="AJ379" t="inlineStr"/>
       <c r="AK379" t="inlineStr"/>
       <c r="AL379" t="inlineStr"/>
+      <c r="AM379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -33067,6 +33522,7 @@
       <c r="AJ380" t="inlineStr"/>
       <c r="AK380" t="inlineStr"/>
       <c r="AL380" t="inlineStr"/>
+      <c r="AM380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -33203,6 +33659,9 @@
         </is>
       </c>
       <c r="AL381" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM381" t="n">
         <v>1</v>
       </c>
     </row>
@@ -33279,6 +33738,7 @@
       <c r="AJ382" t="inlineStr"/>
       <c r="AK382" t="inlineStr"/>
       <c r="AL382" t="inlineStr"/>
+      <c r="AM382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -33349,6 +33809,7 @@
       <c r="AJ383" t="inlineStr"/>
       <c r="AK383" t="inlineStr"/>
       <c r="AL383" t="inlineStr"/>
+      <c r="AM383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" t="n">
@@ -33439,6 +33900,7 @@
       <c r="AJ384" t="inlineStr"/>
       <c r="AK384" t="inlineStr"/>
       <c r="AL384" t="inlineStr"/>
+      <c r="AM384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -33513,6 +33975,7 @@
       <c r="AJ385" t="inlineStr"/>
       <c r="AK385" t="inlineStr"/>
       <c r="AL385" t="inlineStr"/>
+      <c r="AM385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -33583,6 +34046,7 @@
       <c r="AJ386" t="inlineStr"/>
       <c r="AK386" t="inlineStr"/>
       <c r="AL386" t="inlineStr"/>
+      <c r="AM386" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -33653,6 +34117,7 @@
       <c r="AJ387" t="inlineStr"/>
       <c r="AK387" t="inlineStr"/>
       <c r="AL387" t="inlineStr"/>
+      <c r="AM387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -33723,6 +34188,7 @@
       <c r="AJ388" t="inlineStr"/>
       <c r="AK388" t="inlineStr"/>
       <c r="AL388" t="inlineStr"/>
+      <c r="AM388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -33811,6 +34277,7 @@
       <c r="AJ389" t="inlineStr"/>
       <c r="AK389" t="inlineStr"/>
       <c r="AL389" t="inlineStr"/>
+      <c r="AM389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" t="n">
@@ -33897,6 +34364,7 @@
       <c r="AJ390" t="inlineStr"/>
       <c r="AK390" t="inlineStr"/>
       <c r="AL390" t="inlineStr"/>
+      <c r="AM390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" t="n">
@@ -34033,6 +34501,9 @@
         </is>
       </c>
       <c r="AL391" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM391" t="n">
         <v>1</v>
       </c>
     </row>
@@ -34109,6 +34580,7 @@
       <c r="AJ392" t="inlineStr"/>
       <c r="AK392" t="inlineStr"/>
       <c r="AL392" t="inlineStr"/>
+      <c r="AM392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -34203,6 +34675,7 @@
       <c r="AJ393" t="inlineStr"/>
       <c r="AK393" t="inlineStr"/>
       <c r="AL393" t="inlineStr"/>
+      <c r="AM393" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" t="n">
@@ -34273,6 +34746,7 @@
       <c r="AJ394" t="inlineStr"/>
       <c r="AK394" t="inlineStr"/>
       <c r="AL394" t="inlineStr"/>
+      <c r="AM394" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -34367,6 +34841,7 @@
       <c r="AJ395" t="inlineStr"/>
       <c r="AK395" t="inlineStr"/>
       <c r="AL395" t="inlineStr"/>
+      <c r="AM395" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -34437,6 +34912,7 @@
       <c r="AJ396" t="inlineStr"/>
       <c r="AK396" t="inlineStr"/>
       <c r="AL396" t="inlineStr"/>
+      <c r="AM396" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -34593,6 +35069,9 @@
         </is>
       </c>
       <c r="AL397" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM397" t="n">
         <v>1</v>
       </c>
     </row>
@@ -34665,6 +35144,7 @@
       <c r="AJ398" t="inlineStr"/>
       <c r="AK398" t="inlineStr"/>
       <c r="AL398" t="inlineStr"/>
+      <c r="AM398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -34735,6 +35215,7 @@
       <c r="AJ399" t="inlineStr"/>
       <c r="AK399" t="inlineStr"/>
       <c r="AL399" t="inlineStr"/>
+      <c r="AM399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -34825,6 +35306,7 @@
       <c r="AJ400" t="inlineStr"/>
       <c r="AK400" t="inlineStr"/>
       <c r="AL400" t="inlineStr"/>
+      <c r="AM400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" t="n">
@@ -34913,6 +35395,7 @@
       <c r="AJ401" t="inlineStr"/>
       <c r="AK401" t="inlineStr"/>
       <c r="AL401" t="inlineStr"/>
+      <c r="AM401" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" t="n">
@@ -34989,6 +35472,7 @@
       <c r="AJ402" t="inlineStr"/>
       <c r="AK402" t="inlineStr"/>
       <c r="AL402" t="inlineStr"/>
+      <c r="AM402" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" t="n">
@@ -35085,6 +35569,7 @@
       <c r="AJ403" t="inlineStr"/>
       <c r="AK403" t="inlineStr"/>
       <c r="AL403" t="inlineStr"/>
+      <c r="AM403" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" t="n">
@@ -35175,6 +35660,7 @@
       <c r="AJ404" t="inlineStr"/>
       <c r="AK404" t="inlineStr"/>
       <c r="AL404" t="inlineStr"/>
+      <c r="AM404" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" t="n">
@@ -35263,6 +35749,7 @@
       <c r="AJ405" t="inlineStr"/>
       <c r="AK405" t="inlineStr"/>
       <c r="AL405" t="inlineStr"/>
+      <c r="AM405" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" t="n">
@@ -35359,6 +35846,7 @@
       <c r="AJ406" t="inlineStr"/>
       <c r="AK406" t="inlineStr"/>
       <c r="AL406" t="inlineStr"/>
+      <c r="AM406" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
